--- a/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026 ELK ANTLERLESS CWMU ANY LEGAL WEAPON.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026 ELK ANTLERLESS CWMU ANY LEGAL WEAPON.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O60"/>
+  <dimension ref="A1:P60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -577,10 +577,15 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Average Age Harvested (previous hunting season)</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
+          <t>Average Harvest Age</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Current Age (3-Yr Avg)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Avg Days Hunted (previous hunting season)</t>
         </is>
@@ -649,7 +654,8 @@
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>7.2</t>
         </is>
@@ -718,7 +724,8 @@
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr"/>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>2.4</t>
         </is>
@@ -787,7 +794,8 @@
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -856,7 +864,8 @@
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr"/>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
@@ -925,7 +934,8 @@
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>6.2</t>
         </is>
@@ -994,7 +1004,8 @@
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr"/>
-      <c r="O7" s="3" t="inlineStr">
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -1063,7 +1074,8 @@
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
@@ -1132,7 +1144,8 @@
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr"/>
-      <c r="O9" s="3" t="inlineStr">
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" s="3" t="inlineStr">
         <is>
           <t>2.7</t>
         </is>
@@ -1201,7 +1214,8 @@
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr"/>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
@@ -1270,7 +1284,8 @@
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr"/>
-      <c r="O11" s="3" t="inlineStr">
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr">
         <is>
           <t>1.8</t>
         </is>
@@ -1339,7 +1354,8 @@
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr"/>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -1408,7 +1424,8 @@
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr"/>
-      <c r="O13" s="3" t="inlineStr">
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -1477,7 +1494,8 @@
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr"/>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>1.7</t>
         </is>
@@ -1546,7 +1564,8 @@
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr"/>
-      <c r="O15" s="3" t="inlineStr">
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -1615,7 +1634,8 @@
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr"/>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
@@ -1684,7 +1704,8 @@
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr"/>
-      <c r="O17" s="3" t="inlineStr">
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" s="3" t="inlineStr">
         <is>
           <t>2.4</t>
         </is>
@@ -1753,7 +1774,8 @@
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr"/>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
@@ -1822,7 +1844,8 @@
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr"/>
-      <c r="O19" s="3" t="inlineStr">
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" s="3" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
@@ -1891,7 +1914,8 @@
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr"/>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -1960,7 +1984,8 @@
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr"/>
-      <c r="O21" s="3" t="inlineStr">
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" s="3" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
@@ -2029,7 +2054,8 @@
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr"/>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -2098,7 +2124,8 @@
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr"/>
-      <c r="O23" s="3" t="inlineStr">
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" s="3" t="inlineStr">
         <is>
           <t>1.7</t>
         </is>
@@ -2167,7 +2194,8 @@
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr"/>
-      <c r="O24" s="2" t="inlineStr">
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>2.7</t>
         </is>
@@ -2236,7 +2264,8 @@
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr"/>
-      <c r="O25" s="3" t="inlineStr">
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" s="3" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
@@ -2305,7 +2334,8 @@
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr"/>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>3.1</t>
         </is>
@@ -2374,7 +2404,8 @@
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr"/>
-      <c r="O27" s="3" t="inlineStr">
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" s="3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -2443,7 +2474,8 @@
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr"/>
-      <c r="O28" s="2" t="inlineStr">
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -2512,7 +2544,8 @@
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr"/>
-      <c r="O29" s="3" t="inlineStr">
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" s="3" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
@@ -2581,7 +2614,8 @@
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr"/>
-      <c r="O30" s="2" t="inlineStr">
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" s="2" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
@@ -2650,7 +2684,8 @@
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr"/>
-      <c r="O31" s="3" t="inlineStr">
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" s="3" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
@@ -2719,7 +2754,8 @@
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr"/>
-      <c r="O32" s="2" t="inlineStr">
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" s="2" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
@@ -2788,7 +2824,8 @@
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr"/>
-      <c r="O33" s="3" t="inlineStr">
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" s="3" t="inlineStr">
         <is>
           <t>1.8</t>
         </is>
@@ -2857,7 +2894,8 @@
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr"/>
-      <c r="O34" s="2" t="inlineStr">
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -2926,7 +2964,8 @@
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr"/>
-      <c r="O35" s="3" t="inlineStr">
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" s="3" t="inlineStr">
         <is>
           <t>1.9</t>
         </is>
@@ -2995,7 +3034,8 @@
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr"/>
-      <c r="O36" s="2" t="inlineStr">
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -3064,7 +3104,8 @@
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr"/>
-      <c r="O37" s="3" t="inlineStr">
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" s="3" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -3133,7 +3174,8 @@
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr"/>
-      <c r="O38" s="2" t="inlineStr">
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" s="2" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
@@ -3202,7 +3244,8 @@
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr"/>
-      <c r="O39" s="3" t="inlineStr">
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" s="3" t="inlineStr">
         <is>
           <t>2.4</t>
         </is>
@@ -3271,7 +3314,8 @@
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr"/>
-      <c r="O40" s="2" t="inlineStr">
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" s="2" t="inlineStr">
         <is>
           <t>1.9</t>
         </is>
@@ -3340,7 +3384,8 @@
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr"/>
-      <c r="O41" s="3" t="inlineStr">
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" s="3" t="inlineStr">
         <is>
           <t>3.7</t>
         </is>
@@ -3409,7 +3454,8 @@
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr"/>
-      <c r="O42" s="2" t="inlineStr">
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -3478,7 +3524,8 @@
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr"/>
-      <c r="O43" s="3" t="inlineStr">
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" s="3" t="inlineStr">
         <is>
           <t>3.8</t>
         </is>
@@ -3547,7 +3594,8 @@
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr"/>
-      <c r="O44" s="2" t="inlineStr">
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" s="2" t="inlineStr">
         <is>
           <t>11.5</t>
         </is>
@@ -3616,7 +3664,8 @@
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr"/>
-      <c r="O45" s="3" t="inlineStr">
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" s="3" t="inlineStr">
         <is>
           <t>1.7</t>
         </is>
@@ -3685,7 +3734,8 @@
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr"/>
-      <c r="O46" s="2" t="inlineStr">
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" s="2" t="inlineStr">
         <is>
           <t>2.3</t>
         </is>
@@ -3754,7 +3804,8 @@
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr"/>
-      <c r="O47" s="3" t="inlineStr">
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" s="3" t="inlineStr">
         <is>
           <t>1.9</t>
         </is>
@@ -3823,7 +3874,8 @@
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr"/>
-      <c r="O48" s="2" t="inlineStr">
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -3892,7 +3944,8 @@
         </is>
       </c>
       <c r="N49" s="3" t="inlineStr"/>
-      <c r="O49" s="3" t="inlineStr">
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -3961,7 +4014,8 @@
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr"/>
-      <c r="O50" s="2" t="inlineStr">
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" s="2" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
@@ -4030,7 +4084,8 @@
         </is>
       </c>
       <c r="N51" s="3" t="inlineStr"/>
-      <c r="O51" s="3" t="inlineStr">
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" s="3" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
@@ -4091,7 +4146,8 @@
       <c r="L52" s="2" t="inlineStr"/>
       <c r="M52" s="2" t="inlineStr"/>
       <c r="N52" s="2" t="inlineStr"/>
-      <c r="O52" s="2" t="inlineStr">
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" s="2" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
@@ -4160,7 +4216,8 @@
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr"/>
-      <c r="O53" s="3" t="inlineStr">
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" s="3" t="inlineStr">
         <is>
           <t>1.9</t>
         </is>
@@ -4229,7 +4286,8 @@
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr"/>
-      <c r="O54" s="2" t="inlineStr">
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" s="2" t="inlineStr">
         <is>
           <t>3.6</t>
         </is>
@@ -4298,7 +4356,8 @@
         </is>
       </c>
       <c r="N55" s="3" t="inlineStr"/>
-      <c r="O55" s="3" t="inlineStr">
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" s="3" t="inlineStr">
         <is>
           <t>2.4</t>
         </is>
@@ -4367,7 +4426,8 @@
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr"/>
-      <c r="O56" s="2" t="inlineStr">
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" s="2" t="inlineStr">
         <is>
           <t>2.7</t>
         </is>
@@ -4435,8 +4495,13 @@
           <t>50</t>
         </is>
       </c>
-      <c r="N57" s="3" t="inlineStr"/>
-      <c r="O57" s="3" t="inlineStr">
+      <c r="N57" s="3" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" s="3" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
@@ -4505,7 +4570,8 @@
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr"/>
-      <c r="O58" s="2" t="inlineStr">
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -4574,7 +4640,8 @@
         </is>
       </c>
       <c r="N59" s="3" t="inlineStr"/>
-      <c r="O59" s="3" t="inlineStr">
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" s="3" t="inlineStr">
         <is>
           <t>1.6</t>
         </is>
@@ -4643,7 +4710,8 @@
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr"/>
-      <c r="O60" s="2" t="inlineStr">
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
